--- a/exports/JIOFIN_full_report.xlsx
+++ b/exports/JIOFIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>17.11</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45187.55208333334</v>
+        <v>45189.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>233.6</v>
+        <v>230</v>
       </c>
       <c r="I2" t="n">
         <v>231.5572576122591</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K2" t="n">
-        <v>6.81</v>
+        <v>5.17</v>
       </c>
       <c r="L2" t="n">
         <v>5.24</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.39</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45226.38541666666</v>
+        <v>45226.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>218.75</v>
+        <v>224.6</v>
       </c>
       <c r="I3" t="n">
         <v>218.9537509241986</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>4.89</v>
+        <v>2.35</v>
       </c>
       <c r="L3" t="n">
         <v>2.43</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>7.57</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45247.55208333334</v>
+        <v>45250.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>220.8</v>
+        <v>216.2</v>
       </c>
       <c r="I4" t="n">
         <v>216.4227423349507</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.69</v>
+        <v>-3.74</v>
       </c>
       <c r="L4" t="n">
         <v>4.81</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>6.39</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45254.38541666666</v>
+        <v>45254.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>224.6</v>
+        <v>227</v>
       </c>
       <c r="I5" t="n">
         <v>226.4347062540388</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.89</v>
+        <v>-5</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>5.39</v>
       </c>
       <c r="M5" t="n">
         <v>0.88</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>5.93</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>243.35</v>
+        <v>231.5</v>
       </c>
       <c r="I6" t="n">
         <v>233.4156106735535</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K6" t="n">
-        <v>7.2</v>
+        <v>1.98</v>
       </c>
       <c r="L6" t="n">
         <v>1.92</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45295.55208333334</v>
+        <v>45296.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>241.65</v>
+        <v>244.05</v>
       </c>
       <c r="I7" t="n">
         <v>243.2483844189779</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.38</v>
+        <v>-5.42</v>
       </c>
       <c r="L7" t="n">
-        <v>5.38</v>
+        <v>7.21</v>
       </c>
       <c r="M7" t="n">
         <v>1.86</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>4.01</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45306.55208333334</v>
+        <v>45307.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>267.35</v>
+        <v>247.35</v>
       </c>
       <c r="I8" t="n">
         <v>251.7204562930535</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>9.550000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="L8" t="n">
         <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04</v>
+        <v>4.96</v>
       </c>
       <c r="N8" t="n">
-        <v>0.45</v>
+        <v>6.7</v>
       </c>
       <c r="O8" t="n">
         <v>0.8100000000000001</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.13</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45316.55208333334</v>
+        <v>45320.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>239.95</v>
+        <v>254.1</v>
       </c>
       <c r="I9" t="n">
         <v>252.0672671534966</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>2.99</v>
+        <v>-2.73</v>
       </c>
       <c r="L9" t="n">
         <v>4.31</v>
@@ -954,7 +1061,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.19</v>
+        <v>4.71</v>
       </c>
       <c r="O9" t="n">
         <v>-6.7</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.84</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>339.5</v>
+        <v>328.4</v>
       </c>
       <c r="I10" t="n">
         <v>333.4855237057873</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>33.61</v>
+        <v>29.24</v>
       </c>
       <c r="L10" t="n">
         <v>5.55</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>13.56</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45387.38541666666</v>
+        <v>45387.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>369.4</v>
+        <v>373.2</v>
       </c>
       <c r="I11" t="n">
         <v>371.649397896633</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.48</v>
+        <v>-13.64</v>
       </c>
       <c r="L11" t="n">
-        <v>14.01</v>
+        <v>14.14</v>
       </c>
       <c r="M11" t="n">
         <v>1.95</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>371</v>
+        <v>354.7</v>
       </c>
       <c r="I12" t="n">
         <v>363.2381587679756</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.59</v>
+        <v>-4.96</v>
       </c>
       <c r="L12" t="n">
         <v>5.95</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45434.55208333334</v>
+        <v>45435.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>357.25</v>
+        <v>372.8</v>
       </c>
       <c r="I13" t="n">
         <v>364.6714986583605</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.72</v>
+        <v>-5.1</v>
       </c>
       <c r="L13" t="n">
-        <v>4.51</v>
+        <v>6.01</v>
       </c>
       <c r="M13" t="n">
         <v>0.58</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.95</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45441.38541666666</v>
+        <v>45441.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>350.65</v>
+        <v>349.65</v>
       </c>
       <c r="I14" t="n">
         <v>349.7418107843696</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.94</v>
+        <v>-6.21</v>
       </c>
       <c r="L14" t="n">
-        <v>6.12</v>
+        <v>6.63</v>
       </c>
       <c r="M14" t="n">
         <v>0.53</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.95</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45463.38541666666</v>
+        <v>45463.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>361.5</v>
+        <v>365.45</v>
       </c>
       <c r="I15" t="n">
         <v>364.1518577899727</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>21.83333333333333</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.39</v>
+        <v>-4.52</v>
       </c>
       <c r="L15" t="n">
         <v>5.33</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45489.55208333334</v>
+        <v>45491.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>344.8</v>
+        <v>337.9</v>
       </c>
       <c r="I16" t="n">
         <v>344.0291798720635</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>26</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.65</v>
+        <v>-7.54</v>
       </c>
       <c r="L16" t="n">
-        <v>6.12</v>
+        <v>7.8</v>
       </c>
       <c r="M16" t="n">
         <v>1.42</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.52</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45511.38541666666</v>
+        <v>45511.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>324.25</v>
+        <v>331</v>
       </c>
       <c r="I17" t="n">
         <v>327.9482349492728</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>4.04</v>
+        <v>2.04</v>
       </c>
       <c r="L17" t="n">
         <v>2.44</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.49</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45569.38541666666</v>
+        <v>45569.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>341.6</v>
+        <v>338.05</v>
       </c>
       <c r="I18" t="n">
         <v>338.4248051235302</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>57.83333333333334</v>
+        <v>58</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>2.13</v>
       </c>
       <c r="L18" t="n">
         <v>3.56</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.69</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45609.55208333334</v>
+        <v>45610.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>300.4</v>
+        <v>315</v>
       </c>
       <c r="I19" t="n">
         <v>314.9765138894996</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>40</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K19" t="n">
-        <v>11.14</v>
+        <v>6.82</v>
       </c>
       <c r="L19" t="n">
         <v>3.45</v>
@@ -1524,7 +1751,7 @@
         <v>2.38</v>
       </c>
       <c r="N19" t="n">
-        <v>2.91</v>
+        <v>6.39</v>
       </c>
       <c r="O19" t="n">
         <v>-2.24</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.24</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>336.75</v>
+        <v>326.5</v>
       </c>
       <c r="I20" t="n">
         <v>329.5164074976884</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K20" t="n">
-        <v>6.9</v>
+        <v>3.65</v>
       </c>
       <c r="L20" t="n">
         <v>3.89</v>
@@ -1581,7 +1820,7 @@
         <v>0.72</v>
       </c>
       <c r="N20" t="n">
-        <v>1.5</v>
+        <v>3.49</v>
       </c>
       <c r="O20" t="n">
         <v>6.39</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.99</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45692.55208333334</v>
+        <v>45693.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>244.8</v>
+        <v>253.99</v>
       </c>
       <c r="I21" t="n">
         <v>251.5585047713905</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K21" t="n">
-        <v>25.02</v>
+        <v>22.21</v>
       </c>
       <c r="L21" t="n">
         <v>3.22</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>8.77</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45699.55208333334</v>
+        <v>45700.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>236.5</v>
+        <v>230.7</v>
       </c>
       <c r="I22" t="n">
         <v>233.2794102175416</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.89</v>
+        <v>-9.17</v>
       </c>
       <c r="L22" t="n">
-        <v>7.58</v>
+        <v>12.11</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="N22" t="n">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="O22" t="n">
         <v>1.88</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>7</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>217.5</v>
+        <v>219.76</v>
       </c>
       <c r="I23" t="n">
         <v>219.0649292518902</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K23" t="n">
-        <v>5.72</v>
+        <v>4.74</v>
       </c>
       <c r="L23" t="n">
         <v>3.4</v>
       </c>
       <c r="M23" t="n">
-        <v>0.92</v>
+        <v>2.07</v>
       </c>
       <c r="N23" t="n">
         <v>5.45</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>7.56</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>222.54</v>
+        <v>210</v>
       </c>
       <c r="I24" t="n">
         <v>220.1598044610704</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K24" t="n">
-        <v>1.27</v>
+        <v>-4.44</v>
       </c>
       <c r="L24" t="n">
-        <v>3.07</v>
+        <v>7.58</v>
       </c>
       <c r="M24" t="n">
-        <v>1.71</v>
+        <v>8.74</v>
       </c>
       <c r="N24" t="n">
         <v>3.52</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>7.88</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>221.1</v>
+        <v>229.73</v>
       </c>
       <c r="I25" t="n">
         <v>226.5425682170932</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.29</v>
+        <v>-9.4</v>
       </c>
       <c r="L25" t="n">
-        <v>7.38</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>0.98</v>
+        <v>2.12</v>
       </c>
       <c r="N25" t="n">
         <v>4.93</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>9.08</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45785.55208333334</v>
+        <v>45786.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>250.05</v>
+        <v>247.3</v>
       </c>
       <c r="I26" t="n">
         <v>247.5473914521039</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K26" t="n">
-        <v>8.85</v>
+        <v>7.65</v>
       </c>
       <c r="L26" t="n">
         <v>2.62</v>
       </c>
       <c r="M26" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="N26" t="n">
         <v>3.63</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>6.18</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>261.05</v>
+        <v>263</v>
       </c>
       <c r="I27" t="n">
         <v>262.5778524878722</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.56</v>
+        <v>-6.35</v>
       </c>
       <c r="L27" t="n">
-        <v>6.35</v>
+        <v>6.55</v>
       </c>
       <c r="M27" t="n">
         <v>3.91</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.98</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45825.38541666666</v>
+        <v>45825.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>291.1</v>
+        <v>289.8</v>
       </c>
       <c r="I28" t="n">
         <v>290.6206179565878</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K28" t="n">
-        <v>10.68</v>
+        <v>10.19</v>
       </c>
       <c r="L28" t="n">
         <v>0.74</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,25 +2420,25 @@
         <v>5.08</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>292.8</v>
+        <v>303.75</v>
       </c>
       <c r="I29" t="n">
         <v>297.9364777253101</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.04</v>
+        <v>-4.81</v>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>5.04</v>
       </c>
       <c r="M29" t="n">
-        <v>0.61</v>
+        <v>1.78</v>
       </c>
       <c r="N29" t="n">
         <v>3.55</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.42</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45849.55208333334</v>
+        <v>45852.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>325.4</v>
+        <v>318.4</v>
       </c>
       <c r="I30" t="n">
         <v>319.3860672989257</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K30" t="n">
-        <v>7.13</v>
+        <v>4.82</v>
       </c>
       <c r="L30" t="n">
         <v>2.19</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>5.86</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45868.55208333334</v>
+        <v>45869.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>320</v>
+        <v>330.5</v>
       </c>
       <c r="I31" t="n">
         <v>322.6506569139866</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.5</v>
+        <v>-3.8</v>
       </c>
       <c r="L31" t="n">
-        <v>2.92</v>
+        <v>4.18</v>
       </c>
       <c r="M31" t="n">
         <v>0.68</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>7.33</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45875.55208333334</v>
+        <v>45876.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>326.2</v>
+        <v>318.2</v>
       </c>
       <c r="I32" t="n">
         <v>318.6431475605448</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.3</v>
+        <v>-3.72</v>
       </c>
       <c r="L32" t="n">
         <v>4.25</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="N32" t="n">
         <v>1.94</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.33</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45936.38541666666</v>
+        <v>45936.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>303.4</v>
+        <v>306.1</v>
       </c>
       <c r="I33" t="n">
         <v>304.1598966314849</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>60</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
         <v>4.87</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>4.11</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45965.38541666666</v>
+        <v>45965.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>303.3</v>
+        <v>302.1</v>
       </c>
       <c r="I34" t="n">
         <v>302.3068606595049</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.91</v>
+        <v>-1.31</v>
       </c>
       <c r="L34" t="n">
-        <v>1.08</v>
+        <v>1.55</v>
       </c>
       <c r="M34" t="n">
         <v>0.75</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>2.97</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>305.45</v>
+        <v>309.85</v>
       </c>
       <c r="I35" t="n">
         <v>306.2478170415508</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.11</v>
+        <v>-2.57</v>
       </c>
       <c r="L35" t="n">
-        <v>1.18</v>
+        <v>2.71</v>
       </c>
       <c r="M35" t="n">
         <v>0.08</v>
       </c>
       <c r="N35" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
         <v>-1.6</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>4.03</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45982.55208333334</v>
+        <v>45985.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>303.9</v>
+        <v>302.25</v>
       </c>
       <c r="I36" t="n">
         <v>303.2834726406379</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.92</v>
+        <v>-2.45</v>
       </c>
       <c r="L36" t="n">
-        <v>2.21</v>
+        <v>2.65</v>
       </c>
       <c r="M36" t="n">
         <v>0.57</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>3.46</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>295.6</v>
+        <v>302.1</v>
       </c>
       <c r="I37" t="n">
         <v>300.0614461056996</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K37" t="n">
-        <v>2.2</v>
+        <v>0.05</v>
       </c>
       <c r="L37" t="n">
         <v>2.5</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>3.92</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46030.38541666666</v>
+        <v>46030.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>295.4</v>
+        <v>292.65</v>
       </c>
       <c r="I38" t="n">
         <v>293.168976995141</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.22</v>
+        <v>-3.13</v>
       </c>
       <c r="L38" t="n">
-        <v>2.85</v>
+        <v>3.29</v>
       </c>
       <c r="M38" t="n">
         <v>0.22</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>4.85</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>245.15</v>
+        <v>265.3</v>
       </c>
       <c r="I39" t="n">
         <v>259.0257999113722</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>16.23</v>
+        <v>9.35</v>
       </c>
       <c r="L39" t="n">
         <v>0.99</v>
       </c>
       <c r="M39" t="n">
-        <v>1.29</v>
+        <v>6.08</v>
       </c>
       <c r="N39" t="n">
-        <v>1.58</v>
+        <v>7.89</v>
       </c>
       <c r="O39" t="n">
         <v>-3.67</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.1</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46072.38541666666</v>
+        <v>46072.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>260.45</v>
+        <v>257.9</v>
       </c>
       <c r="I40" t="n">
         <v>257.9293523010188</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.83</v>
+        <v>-2.79</v>
       </c>
       <c r="L40" t="n">
         <v>3.15</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>4.53</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46098.55208333334</v>
+        <v>46099.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>237.65</v>
+        <v>248.25</v>
       </c>
       <c r="I41" t="n">
         <v>245.5056219010486</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>7.85</v>
+        <v>3.74</v>
       </c>
       <c r="L41" t="n">
         <v>1.11</v>
@@ -2778,7 +3269,7 @@
         <v>1.91</v>
       </c>
       <c r="N41" t="n">
-        <v>1.78</v>
+        <v>4.57</v>
       </c>
       <c r="O41" t="n">
         <v>-2.27</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>239.25</v>
+        <v>226.25</v>
       </c>
       <c r="I42" t="n">
         <v>233.2421429051025</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.63</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>4.29</v>
+        <v>9</v>
       </c>
       <c r="M42" t="n">
         <v>2.23</v>
       </c>
       <c r="N42" t="n">
-        <v>3.26</v>
+        <v>5.58</v>
       </c>
       <c r="O42" t="n">
         <v>4.57</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>10</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>235.1</v>
+        <v>245.1</v>
       </c>
       <c r="I43" t="n">
         <v>240.5955624396559</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.91</v>
+        <v>-8.33</v>
       </c>
       <c r="L43" t="n">
-        <v>6.52</v>
+        <v>8.91</v>
       </c>
       <c r="M43" t="n">
-        <v>4.01</v>
+        <v>4.25</v>
       </c>
       <c r="N43" t="n">
-        <v>3.68</v>
+        <v>5.49</v>
       </c>
       <c r="O43" t="n">
         <v>-5.58</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.4</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>239.98</v>
+        <v>233.77</v>
       </c>
       <c r="I44" t="n">
         <v>239.0415617494978</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.09</v>
+        <v>-4.62</v>
       </c>
       <c r="L44" t="n">
-        <v>4.49</v>
+        <v>4.86</v>
       </c>
       <c r="M44" t="n">
         <v>2.67</v>
       </c>
       <c r="N44" t="n">
-        <v>3.63</v>
+        <v>3.85</v>
       </c>
       <c r="O44" t="n">
         <v>5.49</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.83</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46167.38541666666</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>241.88</v>
+        <v>241.93</v>
       </c>
       <c r="I45" t="n">
         <v>241.8926727302061</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.47</v>
+        <v>-3.49</v>
       </c>
       <c r="L45" t="n">
         <v>4.23</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>4.39</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46178.55208333334</v>
+        <v>46181.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>237.2</v>
+        <v>232.23</v>
       </c>
       <c r="I46" t="n">
         <v>233.6480822284075</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.96</v>
+        <v>-4.01</v>
       </c>
       <c r="L46" t="n">
         <v>4.27</v>
       </c>
       <c r="M46" t="n">
-        <v>0.72</v>
+        <v>1.77</v>
       </c>
       <c r="N46" t="n">
-        <v>2.17</v>
+        <v>3.8</v>
       </c>
       <c r="O46" t="n">
         <v>1.35</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>4.92</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>236.33</v>
+        <v>241.16</v>
       </c>
       <c r="I47" t="n">
         <v>238.1459048913067</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.77</v>
+        <v>-3.85</v>
       </c>
       <c r="L47" t="n">
-        <v>1.84</v>
+        <v>4.93</v>
       </c>
       <c r="M47" t="n">
-        <v>1.18</v>
+        <v>2.19</v>
       </c>
       <c r="N47" t="n">
         <v>3.56</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>4.73</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>236.05</v>
+        <v>230.86</v>
       </c>
       <c r="I48" t="n">
         <v>234.8902510278509</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.12</v>
+        <v>-4.27</v>
       </c>
       <c r="L48" t="n">
-        <v>2.46</v>
+        <v>5.04</v>
       </c>
       <c r="M48" t="n">
         <v>0.42</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>5.43</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46219.55208333334</v>
+        <v>46220.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>235.98</v>
+        <v>244.3</v>
       </c>
       <c r="I49" t="n">
         <v>243.2171470006967</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.22</v>
+        <v>-5.82</v>
       </c>
       <c r="L49" t="n">
-        <v>5.48</v>
+        <v>8.27</v>
       </c>
       <c r="M49" t="n">
-        <v>0.54</v>
+        <v>4.88</v>
       </c>
       <c r="N49" t="n">
         <v>3.74</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>4.25</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46225.55208333334</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>234.89</v>
+        <v>233.04</v>
       </c>
       <c r="I50" t="n">
         <v>233.9141385244741</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.85</v>
+        <v>-4.61</v>
       </c>
       <c r="L50" t="n">
-        <v>4.14</v>
+        <v>4.63</v>
       </c>
       <c r="M50" t="n">
         <v>0.49</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>5.21</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>237.25</v>
+        <v>253.07</v>
       </c>
       <c r="I51" t="n">
         <v>243.3436544191195</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.81</v>
+        <v>-8.6</v>
       </c>
       <c r="L51" t="n">
-        <v>2.65</v>
+        <v>8.75</v>
       </c>
       <c r="M51" t="n">
         <v>0.86</v>
       </c>
       <c r="N51" t="n">
-        <v>0.72</v>
+        <v>4.79</v>
       </c>
       <c r="O51" t="n">
         <v>-0.68</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.9</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46248.38541666666</v>
+        <v>46248.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>250.9</v>
+        <v>249.7</v>
       </c>
       <c r="I52" t="n">
         <v>250.811387289578</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.86</v>
+        <v>-1.33</v>
       </c>
       <c r="L52" t="n">
         <v>6.15</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3465,6 +4100,14 @@
       <c r="Q53" t="n">
         <v>99</v>
       </c>
+      <c r="R53" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4921,7 +5564,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.2</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="6">
@@ -4931,7 +5574,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -4941,7 +5584,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="8">
@@ -4951,7 +5594,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -4961,7 +5604,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="10">
@@ -4971,7 +5614,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38.2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -4981,7 +5624,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -4991,7 +5634,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -5001,7 +5644,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78.40000000000001</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="14">
@@ -5011,7 +5654,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.67</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="15">
@@ -5021,7 +5664,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.99</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="16">
@@ -5031,7 +5674,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.33</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="17">
@@ -5041,7 +5684,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>33.61</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="18">
@@ -5051,7 +5694,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39.2</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="19">
@@ -5061,7 +5704,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="20">
@@ -5071,7 +5714,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.89</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="21">
@@ -5081,7 +5724,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.01</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="22">
@@ -5091,7 +5734,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -5101,7 +5744,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -5111,7 +5754,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="25">
@@ -5121,7 +5764,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.67</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="26">
@@ -5131,7 +5774,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.15</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="27">
@@ -5151,7 +5794,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
